--- a/data/Linktri/JOB SETS.xlsx
+++ b/data/Linktri/JOB SETS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Windower\addons\GearSwap\data\Linktri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D27EBB-7B0E-4364-9599-5EC87E33FEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC26D2B5-BFC6-428E-859A-40F246B781EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49650" yWindow="1530" windowWidth="19980" windowHeight="16875" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
+    <workbookView xWindow="48210" yWindow="1380" windowWidth="19980" windowHeight="16875" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -194,7 +194,158 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="8"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="4"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1726,6 +1877,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="B3:P24">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Reforged +4">
+      <formula>NOT(ISERROR(SEARCH("Reforged +4",B3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Reforged +3">
+      <formula>NOT(ISERROR(SEARCH("Reforged +3",B3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Reforged +2">
+      <formula>NOT(ISERROR(SEARCH("Reforged +2",B3)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"Reforged +1"</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="base">
+      <formula>NOT(ISERROR(SEARCH("base",B3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Linktri/JOB SETS.xlsx
+++ b/data/Linktri/JOB SETS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Windower\addons\GearSwap\data\Linktri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC26D2B5-BFC6-428E-859A-40F246B781EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE7728B-2B79-4FB0-97ED-00E492BF6FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="48210" yWindow="1380" windowWidth="19980" windowHeight="16875" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
+    <workbookView xWindow="54390" yWindow="1305" windowWidth="19980" windowHeight="16875" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="46">
   <si>
     <t>RDM</t>
   </si>
@@ -144,14 +144,55 @@
   </si>
   <si>
     <t>Reforged +2</t>
+  </si>
+  <si>
+    <t>Head - W.</t>
+  </si>
+  <si>
+    <t>Body - A.</t>
+  </si>
+  <si>
+    <t>Hands - B.</t>
+  </si>
+  <si>
+    <t>Legs - J.</t>
+  </si>
+  <si>
+    <t>Feet - S.</t>
+  </si>
+  <si>
+    <t>1 - San d'Oria</t>
+  </si>
+  <si>
+    <t>4 - Windurst</t>
+  </si>
+  <si>
+    <t>1 - Bastok</t>
+  </si>
+  <si>
+    <t>Cards</t>
+  </si>
+  <si>
+    <t>3 - Jeuno</t>
+  </si>
+  <si>
+    <t>3 - All</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -185,11 +226,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,16 +718,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7EE6E90-D5C2-4C77-92D1-5CD8FC83F1E3}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="16" width="12.7109375" customWidth="1"/>
+    <col min="3" max="17" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
@@ -698,7 +738,7 @@
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>12</v>
@@ -713,7 +753,7 @@
         <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>13</v>
@@ -727,61 +767,64 @@
       <c r="P1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
@@ -810,7 +853,7 @@
         <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M3" t="s">
         <v>15</v>
@@ -824,14 +867,14 @@
       <c r="P3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
@@ -860,7 +903,7 @@
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M4" t="s">
         <v>15</v>
@@ -874,14 +917,14 @@
       <c r="P4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
@@ -910,7 +953,7 @@
         <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M5" t="s">
         <v>15</v>
@@ -924,14 +967,14 @@
       <c r="P5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
@@ -960,7 +1003,7 @@
         <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M6" t="s">
         <v>15</v>
@@ -974,14 +1017,14 @@
       <c r="P6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
       <c r="C7" t="s">
         <v>15</v>
       </c>
@@ -995,22 +1038,22 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
       </c>
-      <c r="I7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="I7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7" t="s">
         <v>15</v>
@@ -1024,14 +1067,14 @@
       <c r="P7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
@@ -1060,7 +1103,7 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M8" t="s">
         <v>15</v>
@@ -1074,14 +1117,14 @@
       <c r="P8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
@@ -1110,7 +1153,7 @@
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
         <v>15</v>
@@ -1124,14 +1167,14 @@
       <c r="P9" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
@@ -1160,7 +1203,7 @@
         <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M10" t="s">
         <v>15</v>
@@ -1174,14 +1217,14 @@
       <c r="P10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
@@ -1195,22 +1238,22 @@
         <v>16</v>
       </c>
       <c r="G11" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K11" t="s">
-        <v>33</v>
-      </c>
-      <c r="L11" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M11" t="s">
         <v>15</v>
@@ -1224,14 +1267,14 @@
       <c r="P11" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
@@ -1260,7 +1303,7 @@
         <v>14</v>
       </c>
       <c r="L12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M12" t="s">
         <v>15</v>
@@ -1274,14 +1317,14 @@
       <c r="P12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
       <c r="C13" t="s">
         <v>16</v>
       </c>
@@ -1295,23 +1338,23 @@
         <v>16</v>
       </c>
       <c r="G13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L13" t="s">
-        <v>15</v>
-      </c>
       <c r="M13" t="s">
         <v>15</v>
       </c>
@@ -1324,14 +1367,14 @@
       <c r="P13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
@@ -1345,7 +1388,7 @@
         <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -1374,14 +1417,14 @@
       <c r="P14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
       <c r="C15" t="s">
         <v>16</v>
       </c>
@@ -1395,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="s">
         <v>15</v>
@@ -1424,14 +1467,14 @@
       <c r="P15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
       <c r="C16" t="s">
         <v>16</v>
       </c>
@@ -1445,12 +1488,12 @@
         <v>16</v>
       </c>
       <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="I16" s="2" t="s">
         <v>33</v>
       </c>
       <c r="J16" t="s">
@@ -1460,7 +1503,7 @@
         <v>33</v>
       </c>
       <c r="L16" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="M16" t="s">
         <v>15</v>
@@ -1474,14 +1517,14 @@
       <c r="P16" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
       <c r="C17" t="s">
         <v>16</v>
       </c>
@@ -1495,7 +1538,7 @@
         <v>16</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -1524,14 +1567,14 @@
       <c r="P17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18" t="s">
-        <v>34</v>
-      </c>
       <c r="C18" t="s">
         <v>34</v>
       </c>
@@ -1545,12 +1588,12 @@
         <v>34</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J18" t="s">
@@ -1560,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="L18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M18" t="s">
         <v>15</v>
@@ -1574,14 +1617,14 @@
       <c r="P18" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
       <c r="C19" t="s">
         <v>16</v>
       </c>
@@ -1595,7 +1638,7 @@
         <v>16</v>
       </c>
       <c r="G19" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H19" t="s">
         <v>33</v>
@@ -1610,7 +1653,7 @@
         <v>33</v>
       </c>
       <c r="L19" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="M19" t="s">
         <v>15</v>
@@ -1624,14 +1667,14 @@
       <c r="P19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" t="s">
-        <v>15</v>
-      </c>
       <c r="C20" t="s">
         <v>15</v>
       </c>
@@ -1674,14 +1717,14 @@
       <c r="P20" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
@@ -1710,7 +1753,7 @@
         <v>14</v>
       </c>
       <c r="L21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M21" t="s">
         <v>15</v>
@@ -1724,14 +1767,14 @@
       <c r="P21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" t="s">
-        <v>14</v>
-      </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
@@ -1745,7 +1788,7 @@
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -1774,14 +1817,14 @@
       <c r="P22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>14</v>
-      </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
@@ -1810,7 +1853,7 @@
         <v>14</v>
       </c>
       <c r="L23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M23" t="s">
         <v>15</v>
@@ -1824,14 +1867,14 @@
       <c r="P23" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>32</v>
       </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
       <c r="C24" t="s">
         <v>16</v>
       </c>
@@ -1847,20 +1890,20 @@
       <c r="G24" t="s">
         <v>16</v>
       </c>
-      <c r="H24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="H24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J24" t="s">
         <v>16</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="L24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M24" t="s">
         <v>15</v>
@@ -1874,24 +1917,44 @@
       <c r="P24" t="s">
         <v>15</v>
       </c>
+      <c r="Q24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="H25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B3:P24">
-    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Reforged +4">
-      <formula>NOT(ISERROR(SEARCH("Reforged +4",B3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Reforged +3">
-      <formula>NOT(ISERROR(SEARCH("Reforged +3",B3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Reforged +2">
-      <formula>NOT(ISERROR(SEARCH("Reforged +2",B3)))</formula>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="H25:L25 C3:Q24">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="base">
+      <formula>NOT(ISERROR(SEARCH("base",C3)))</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Reforged +1"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="base">
-      <formula>NOT(ISERROR(SEARCH("base",B3)))</formula>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Reforged +2">
+      <formula>NOT(ISERROR(SEARCH("Reforged +2",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Reforged +3">
+      <formula>NOT(ISERROR(SEARCH("Reforged +3",C3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="Reforged +4">
+      <formula>NOT(ISERROR(SEARCH("Reforged +4",C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/Linktri/JOB SETS.xlsx
+++ b/data/Linktri/JOB SETS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Windower\addons\GearSwap\data\Linktri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE7728B-2B79-4FB0-97ED-00E492BF6FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F65855E-0D68-4E3B-B8CB-75D2C4CFBAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="54390" yWindow="1305" windowWidth="19980" windowHeight="16875" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
+    <workbookView xWindow="53280" yWindow="1350" windowWidth="19980" windowHeight="16860" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -167,6 +167,9 @@
     <t>4 - Windurst</t>
   </si>
   <si>
+    <t>4 - All</t>
+  </si>
+  <si>
     <t>1 - Bastok</t>
   </si>
   <si>
@@ -174,9 +177,6 @@
   </si>
   <si>
     <t>3 - Jeuno</t>
-  </si>
-  <si>
-    <t>3 - All</t>
   </si>
 </sst>
 </file>
@@ -773,7 +773,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -1926,13 +1926,13 @@
         <v>41</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>40</v>

--- a/data/Linktri/JOB SETS.xlsx
+++ b/data/Linktri/JOB SETS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Windower\addons\GearSwap\data\Linktri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F65855E-0D68-4E3B-B8CB-75D2C4CFBAD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F54F4D4-E9F2-499D-90B5-02F6CAD26DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="53280" yWindow="1350" windowWidth="19980" windowHeight="16860" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
+    <workbookView xWindow="41010" yWindow="1530" windowWidth="19980" windowHeight="16860" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="45">
   <si>
     <t>RDM</t>
   </si>
@@ -168,9 +168,6 @@
   </si>
   <si>
     <t>4 - All</t>
-  </si>
-  <si>
-    <t>1 - Bastok</t>
   </si>
   <si>
     <t>Cards</t>
@@ -773,7 +770,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -825,6 +822,9 @@
       <c r="A3" t="s">
         <v>1</v>
       </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
       <c r="C3" t="s">
         <v>14</v>
       </c>
@@ -875,6 +875,9 @@
       <c r="A4" t="s">
         <v>2</v>
       </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
@@ -925,6 +928,9 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
       <c r="C5" t="s">
         <v>14</v>
       </c>
@@ -975,6 +981,9 @@
       <c r="A6" t="s">
         <v>4</v>
       </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
@@ -1025,6 +1034,9 @@
       <c r="A7" t="s">
         <v>0</v>
       </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
       <c r="C7" t="s">
         <v>15</v>
       </c>
@@ -1075,6 +1087,9 @@
       <c r="A8" t="s">
         <v>5</v>
       </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
@@ -1125,6 +1140,9 @@
       <c r="A9" t="s">
         <v>17</v>
       </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
@@ -1175,6 +1193,9 @@
       <c r="A10" t="s">
         <v>18</v>
       </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
@@ -1225,6 +1246,9 @@
       <c r="A11" t="s">
         <v>19</v>
       </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
@@ -1275,6 +1299,9 @@
       <c r="A12" t="s">
         <v>20</v>
       </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
@@ -1325,6 +1352,9 @@
       <c r="A13" t="s">
         <v>21</v>
       </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
       <c r="C13" t="s">
         <v>16</v>
       </c>
@@ -1346,7 +1376,7 @@
       <c r="I13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="K13" s="2" t="s">
@@ -1375,6 +1405,9 @@
       <c r="A14" t="s">
         <v>22</v>
       </c>
+      <c r="B14">
+        <v>31</v>
+      </c>
       <c r="C14" t="s">
         <v>34</v>
       </c>
@@ -1425,6 +1458,9 @@
       <c r="A15" t="s">
         <v>23</v>
       </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
       <c r="C15" t="s">
         <v>16</v>
       </c>
@@ -1475,6 +1511,9 @@
       <c r="A16" t="s">
         <v>24</v>
       </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
       <c r="C16" t="s">
         <v>16</v>
       </c>
@@ -1491,19 +1530,19 @@
         <v>16</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K16" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="L16" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="M16" t="s">
         <v>15</v>
@@ -1525,6 +1564,9 @@
       <c r="A17" t="s">
         <v>25</v>
       </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
       <c r="C17" t="s">
         <v>16</v>
       </c>
@@ -1575,6 +1617,9 @@
       <c r="A18" t="s">
         <v>26</v>
       </c>
+      <c r="B18">
+        <v>10</v>
+      </c>
       <c r="C18" t="s">
         <v>34</v>
       </c>
@@ -1625,6 +1670,9 @@
       <c r="A19" t="s">
         <v>27</v>
       </c>
+      <c r="B19">
+        <v>3</v>
+      </c>
       <c r="C19" t="s">
         <v>16</v>
       </c>
@@ -1675,6 +1723,9 @@
       <c r="A20" t="s">
         <v>28</v>
       </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
       <c r="C20" t="s">
         <v>15</v>
       </c>
@@ -1725,6 +1776,9 @@
       <c r="A21" t="s">
         <v>29</v>
       </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
@@ -1775,6 +1829,9 @@
       <c r="A22" t="s">
         <v>30</v>
       </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
@@ -1825,6 +1882,9 @@
       <c r="A23" t="s">
         <v>31</v>
       </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
@@ -1875,6 +1935,9 @@
       <c r="A24" t="s">
         <v>32</v>
       </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
       <c r="C24" t="s">
         <v>16</v>
       </c>
@@ -1928,11 +1991,9 @@
       <c r="I25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>40</v>

--- a/data/Linktri/JOB SETS.xlsx
+++ b/data/Linktri/JOB SETS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Windower\addons\GearSwap\data\Linktri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F54F4D4-E9F2-499D-90B5-02F6CAD26DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAA0009-F917-43EE-8922-8712E54B629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41010" yWindow="1530" windowWidth="19980" windowHeight="16860" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
+    <workbookView xWindow="51420" yWindow="1530" windowWidth="19980" windowHeight="16860" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1689,19 +1689,19 @@
         <v>16</v>
       </c>
       <c r="H19" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K19" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="L19" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="M19" t="s">
         <v>15</v>

--- a/data/Linktri/JOB SETS.xlsx
+++ b/data/Linktri/JOB SETS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Program Files (x86)\Windower\addons\GearSwap\data\Linktri\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FAA0009-F917-43EE-8922-8712E54B629C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1D3FF8-A178-4CC3-8FD7-E9B864A78374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51420" yWindow="1530" windowWidth="19980" windowHeight="16860" xr2:uid="{4FCCFEB7-9723-434D-9480-268F5F2E7BEA}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="44">
   <si>
     <t>RDM</t>
   </si>
@@ -140,9 +140,6 @@
     <t>RUN</t>
   </si>
   <si>
-    <t>Relic base</t>
-  </si>
-  <si>
     <t>Reforged +2</t>
   </si>
   <si>
@@ -173,7 +170,7 @@
     <t>Cards</t>
   </si>
   <si>
-    <t>3 - Jeuno</t>
+    <t>2 - Jeuno</t>
   </si>
 </sst>
 </file>
@@ -234,7 +231,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="5">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -282,106 +279,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="4"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -770,7 +667,7 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
@@ -788,19 +685,19 @@
         <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>7</v>
@@ -1273,7 +1170,7 @@
       <c r="J11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="L11" s="3" t="s">
@@ -1371,19 +1268,19 @@
         <v>16</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
@@ -1409,19 +1306,19 @@
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -1621,19 +1518,19 @@
         <v>10</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>16</v>
@@ -1986,17 +1883,17 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="H25" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
